--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طلاب.xlsx
@@ -106,16 +106,16 @@
     <t xml:space="preserve">بندر خلف قليل المسيلي الحارثي</t>
   </si>
   <si>
+    <t xml:space="preserve">خالد الطيب علي احمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خالد عبدالله محمد العتيبي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبد الرحمن احمد حميد الكشي الجهني</t>
+  </si>
+  <si>
     <t xml:space="preserve">براء حسن احمد الحازمي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عبدالرحمن صالح محمد العلياني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خالد عبدالله محمد العتيبي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عبد الرحمن احمد حميد الكشي الجهني</t>
   </si>
   <si>
     <t xml:space="preserve">ماجد سعد رتيمان المرواني</t>
@@ -606,7 +606,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -626,7 +626,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -666,7 +666,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طلاب.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>وحدة الإرشاد الأكاديمي والخريجين - نموذج توزيع فترات الإرشاد</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t xml:space="preserve">ماجد سعد رتيمان المرواني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبدالرحمن صالح محمد العلياني</t>
   </si>
 </sst>
 </file>
@@ -606,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طلاب.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>وحدة الإرشاد الأكاديمي والخريجين - نموذج توزيع فترات الإرشاد</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t xml:space="preserve">عبدالرحمن صالح محمد العلياني</t>
+  </si>
+  <si>
+    <t>5000</t>
   </si>
 </sst>
 </file>
@@ -632,7 +635,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -652,7 +655,7 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
